--- a/data/GPSRC Data Project Template.xlsx
+++ b/data/GPSRC Data Project Template.xlsx
@@ -501,6 +501,9 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="7" max="7" width="23.13"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
